--- a/directory/zhengxie/assets/xlsx/self_links.xlsx
+++ b/directory/zhengxie/assets/xlsx/self_links.xlsx
@@ -68,7 +68,7 @@
     <t>http://www.cppcc.gov.cn/images/favicon.ico</t>
   </si>
   <si>
-    <t>中国政协网,http://www.cppcc.gov.cn/</t>
+    <t>中国政协网,https://www.cppcc.gov.cn/</t>
   </si>
   <si>
     <t>市政协</t>
@@ -80,25 +80,25 @@
     <t>直辖市</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.bjzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.bjzx.gov.cn/ </t>
   </si>
   <si>
     <t>天津市政协</t>
   </si>
   <si>
-    <t>官网,http://www.tjszx.gov.cn/</t>
+    <t>官网,https://www.tjszx.gov.cn/</t>
   </si>
   <si>
     <t>上海市政协</t>
   </si>
   <si>
-    <t>官网,http://www.shszx.gov.cn/</t>
+    <t>官网,https://www.shszx.gov.cn/</t>
   </si>
   <si>
     <t>重庆市政协</t>
   </si>
   <si>
-    <t>官网,http://www.cqzx.gov.cn/</t>
+    <t>官网,https://www.cqzx.gov.cn/</t>
   </si>
   <si>
     <t>区政协</t>
@@ -110,7 +110,7 @@
     <t>自治区</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.gxzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.gxzx.gov.cn/ </t>
   </si>
   <si>
     <t>内蒙古自治区政协</t>
@@ -119,25 +119,25 @@
     <t>http://www.nmgzx.gov.cn/favicon.ico</t>
   </si>
   <si>
-    <t>官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
+    <t>官网,https://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
   </si>
   <si>
     <t>宁夏回族自治区政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.nxzx.gov.cn/  </t>
+    <t xml:space="preserve">官网,https://www.nxzx.gov.cn/  </t>
   </si>
   <si>
     <t>西藏自治区政协</t>
   </si>
   <si>
-    <t>官网,http://www.xizangzx.gov.cn</t>
+    <t>官网,https://www.xizangzx.gov.cn</t>
   </si>
   <si>
     <t>新疆维吾尔自治区政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.xjzx.gov.cn/  </t>
+    <t xml:space="preserve">官网,https://www.xjzx.gov.cn/  </t>
   </si>
   <si>
     <t>省政协</t>
@@ -149,19 +149,19 @@
     <t>省级</t>
   </si>
   <si>
-    <t>官网,http://www.ahzx.gov.cn/</t>
+    <t>官网,https://www.ahzx.gov.cn/</t>
   </si>
   <si>
     <t>福建省政协</t>
   </si>
   <si>
-    <t>官网,http://www.fjzx.gov.cn/</t>
+    <t>官网,https://www.fjzx.gov.cn/</t>
   </si>
   <si>
     <t>甘肃省政协</t>
   </si>
   <si>
-    <t>官网,http://www.gszx.gov.cn/</t>
+    <t>官网,https://www.gszx.gov.cn/</t>
   </si>
   <si>
     <t>广东省政协</t>
@@ -170,7 +170,7 @@
     <t>省级,广东</t>
   </si>
   <si>
-    <t>官网,http://www.gdzxb.gov.cn/</t>
+    <t>官网,https://www.gdzxb.gov.cn/</t>
   </si>
   <si>
     <t>贵州省政协</t>
@@ -182,13 +182,13 @@
     <t>海南省政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.hainanzx.gov.cn/default.html </t>
+    <t xml:space="preserve">官网,https://www.hainanzx.gov.cn/default.html </t>
   </si>
   <si>
     <t>河北省政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.hebzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.hebzx.gov.cn/ </t>
   </si>
   <si>
     <t>河南省政协</t>
@@ -197,13 +197,13 @@
     <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
   </si>
   <si>
-    <t>官网,http://www.hnzx.gov.cn/</t>
+    <t>官网,https://www.hnzx.gov.cn/</t>
   </si>
   <si>
     <t>黑龙江省政协</t>
   </si>
   <si>
-    <t>官网,http://www.hljzx.gov.cn/</t>
+    <t>官网,https://www.hljzx.gov.cn/</t>
   </si>
   <si>
     <t>湖北省政协</t>
@@ -224,13 +224,13 @@
     <t>吉林省政协</t>
   </si>
   <si>
-    <t>官网,http://www.jlzx.gov.cn/</t>
+    <t>官网,https://www.jlzx.gov.cn/</t>
   </si>
   <si>
     <t>江苏省政协</t>
   </si>
   <si>
-    <t>官网,http://www.jszx.gov.cn/</t>
+    <t>官网,https://www.jszx.gov.cn/</t>
   </si>
   <si>
     <t>江西省政协</t>
@@ -242,49 +242,49 @@
     <t>辽宁省政协</t>
   </si>
   <si>
-    <t>官网,http://www.lnzx.gov.cn/</t>
+    <t>官网,https://www.lnzx.gov.cn/</t>
   </si>
   <si>
     <t>青海省政协</t>
   </si>
   <si>
-    <t>官网,http://www.qhszx.gov.cn/</t>
+    <t>官网,https://www.qhszx.gov.cn/</t>
   </si>
   <si>
     <t>山东省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sdzx.gov.cn/</t>
+    <t>官网,https://www.sdzx.gov.cn/</t>
   </si>
   <si>
     <t>山西省政协</t>
   </si>
   <si>
-    <t>官网,http://www.shanxizx.gov.cn/</t>
+    <t>官网,https://www.shanxizx.gov.cn/</t>
   </si>
   <si>
     <t>陕西省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sxzx.gov.cn/</t>
+    <t>官网,https://www.sxzx.gov.cn/</t>
   </si>
   <si>
     <t>四川省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sczx.gov.cn/</t>
+    <t>官网,https://www.sczx.gov.cn/</t>
   </si>
   <si>
     <t>云南省政协</t>
   </si>
   <si>
-    <t>官网,http://www.ynzx.gov.cn/</t>
+    <t>官网,https://www.ynzx.gov.cn/</t>
   </si>
   <si>
     <t>浙江省政协</t>
   </si>
   <si>
-    <t>官网,http://www.zjzx.gov.cn/</t>
+    <t>官网,https://www.zjzx.gov.cn/</t>
   </si>
   <si>
     <t>广州市政协</t>
@@ -302,13 +302,13 @@
     <t>深圳市政协</t>
   </si>
   <si>
-    <t>官网,http://www.szzx.gov.cn/</t>
+    <t>官网,https://www.szzx.gov.cn/</t>
   </si>
   <si>
     <t>珠海市政协</t>
   </si>
   <si>
-    <t>官网,http://www.zhzx.gov.cn/</t>
+    <t>官网,https://www.zhzx.gov.cn/</t>
   </si>
   <si>
     <t>汕头市政协</t>
@@ -317,61 +317,61 @@
     <t>地级市,广东,汕头</t>
   </si>
   <si>
-    <t>官网,http://stzx.shantou.gov.cn/</t>
+    <t>官网,https://stzx.shantou.gov.cn/</t>
   </si>
   <si>
     <t>佛山市政协</t>
   </si>
   <si>
-    <t>官网,http://www.fszx.gov.cn/</t>
+    <t>官网,https://www.fszx.gov.cn/</t>
   </si>
   <si>
     <t>韶关市政协</t>
   </si>
   <si>
-    <t>官网,http://www.sgzxb.gov.cn/</t>
+    <t>官网,https://www.sgzxb.gov.cn/</t>
   </si>
   <si>
     <t>河源市政协</t>
   </si>
   <si>
-    <t>官网,http://www.gdhyzx.gov.cn/hyzx/index.html</t>
+    <t>官网,https://www.gdhyzx.gov.cn/hyzx/index.html</t>
   </si>
   <si>
     <t>梅州市政协</t>
   </si>
   <si>
-    <t>官网,http://www.mzzx.gov.cn/</t>
+    <t>官网,https://www.mzzx.gov.cn/</t>
   </si>
   <si>
     <t>惠州市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.huizhou.gov.cn/</t>
+    <t>官网,https://zx.huizhou.gov.cn/</t>
   </si>
   <si>
     <t>汕尾市政协</t>
   </si>
   <si>
-    <t>官网,http://www.swzx.gov.cn/</t>
+    <t>官网,https://www.swzx.gov.cn/</t>
   </si>
   <si>
     <t>东莞市政协</t>
   </si>
   <si>
-    <t>官网,http://dgzx.dg.gov.cn/</t>
+    <t>官网,https://dgzx.dg.gov.cn/</t>
   </si>
   <si>
     <t>中山市政协</t>
   </si>
   <si>
-    <t>官网,http://zszx.zsnews.cn/</t>
+    <t>官网,https://zszx.zsnews.cn/</t>
   </si>
   <si>
     <t>江门市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.jiangmen.cn/</t>
+    <t>官网,https://zx.jiangmen.cn/</t>
   </si>
   <si>
     <t>阳江市政协</t>
@@ -386,37 +386,37 @@
     <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
   </si>
   <si>
-    <t>官网,http://www.gdzjzx.gov.cn/</t>
+    <t>官网,https://www.gdzjzx.gov.cn/</t>
   </si>
   <si>
     <t>茂名市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+    <t>官网,https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
   </si>
   <si>
     <t>肇庆市政协</t>
   </si>
   <si>
-    <t>官网,http://zqzx.gov.cn/index.html</t>
+    <t>官网,https://zqzx.gov.cn/index.html</t>
   </si>
   <si>
     <t>潮州市政协</t>
   </si>
   <si>
-    <t>官网,http://czzx.gov.cn/</t>
+    <t>官网,https://czzx.gov.cn/</t>
   </si>
   <si>
     <t>揭阳市政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.jieyangzhengxie.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.jieyangzhengxie.gov.cn/ </t>
   </si>
   <si>
     <t>云浮市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.yunfu.gov.cn/</t>
+    <t>官网,https://zx.yunfu.gov.cn/</t>
   </si>
   <si>
     <t>哈尔滨市政协</t>
@@ -434,7 +434,7 @@
     <t>地级市,湖北</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.whzx.org.cn/  </t>
+    <t xml:space="preserve">官网,https://www.whzx.org.cn/  </t>
   </si>
   <si>
     <t>金平区政协</t>
@@ -446,7 +446,7 @@
     <t>市辖区,广东,汕头</t>
   </si>
   <si>
-    <t>官网,http://www.jpzx.gov.cn/welcome</t>
+    <t>官网,https://www.jpzx.gov.cn/welcome</t>
   </si>
 </sst>
 </file>
@@ -2573,14 +2573,14 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H56" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H56">
+    <sortState ref="A1:H56">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="H2" r:id="rId2" display="中国政协网,http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="H2" r:id="rId2" display="中国政协网,https://www.cppcc.gov.cn/"/>
     <hyperlink ref="F8" r:id="rId3" display="http://www.nmgzx.gov.cn/favicon.ico"/>
     <hyperlink ref="F34" r:id="rId4" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
     <hyperlink ref="F56" r:id="rId5" display="http://www.jpzx.gov.cn/favicon.ico"/>
